--- a/tools/data_source/module_data.xlsx
+++ b/tools/data_source/module_data.xlsx
@@ -921,63 +921,86 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="4.25" customWidth="1"/>
-    <col min="6" max="7" width="48" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>energy_cost</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>texture_path</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>crew_slots</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chip_slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>core_bridge</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>舰桥</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>飞船核心区域。核心模块被击毁时，飞船判定为沉没。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>res://data/assets/modules/core_bridge.png</t>
+        </is>
+      </c>
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="2">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1"/>
+      <c r="H2">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tools/data_source/module_data.xlsx
+++ b/tools/data_source/module_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AdvanceFour\tools\data_source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AdvanceFour\tools\data_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B53910-B00C-4853-BC99-D07813A52333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F155AE0-0255-495E-8B78-126C28890BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="3975" windowWidth="16050" windowHeight="8025" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Energy" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
     <sheet name="Function" sheetId="5" r:id="rId5"/>
     <sheet name="Core" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
   <si>
     <t>标识</t>
   </si>
@@ -102,9 +115,6 @@
     <t>炮塔贴图路径</t>
   </si>
   <si>
-    <t>炮塔高X宽</t>
-  </si>
-  <si>
     <t>炮塔轴点</t>
   </si>
   <si>
@@ -129,9 +139,6 @@
     <t>res://data/assets/modules/weapon_cannon_turret.png</t>
   </si>
   <si>
-    <t>2x1</t>
-  </si>
-  <si>
     <t>0.5,0.25</t>
   </si>
   <si>
@@ -199,6 +206,115 @@
   </si>
   <si>
     <t>1x1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>energy_cost</t>
+  </si>
+  <si>
+    <t>texture_path</t>
+  </si>
+  <si>
+    <t>crew_slots</t>
+  </si>
+  <si>
+    <t>chip_slots</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="MS UI Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>炮塔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -206,7 +322,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -226,6 +342,67 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans JP"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="MS UI Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="BIZ UDGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -254,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -262,10 +439,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -476,7 +659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -522,7 +705,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
@@ -545,7 +728,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -614,7 +797,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -643,8 +826,8 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="D1" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -676,28 +859,28 @@
       <c r="N1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
@@ -706,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" s="2">
         <v>10</v>
@@ -730,16 +913,16 @@
         <v>180</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="R2" s="2">
         <v>0</v>
@@ -755,7 +938,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -787,22 +970,22 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
@@ -811,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2" s="2">
         <v>10</v>
@@ -831,7 +1014,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -862,19 +1045,19 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
@@ -883,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -892,22 +1075,22 @@
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
@@ -921,78 +1104,54 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>energy_cost</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>texture_path</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>crew_slots</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>chip_slots</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>core_bridge</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>舰桥</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>飞船核心区域。核心模块被击毁时，飞船判定为沉没。</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2x2</t>
-        </is>
+    <row r="1" spans="1:8" ht="14.25">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>res://data/assets/modules/core_bridge.png</t>
-        </is>
+      <c r="F2" t="s">
+        <v>54</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1002,5 +1161,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="11"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>